--- a/2026-06_Walmart_Valuation.xlsx
+++ b/2026-06_Walmart_Valuation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Desktop\CFI\FMVA\Core Course\Practice\Walmart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Desktop\GitHub\Walmart-Equity-Research-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6D8E2F-EBC2-4E1F-A42F-A651EB48AC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0942367E-4123-46FC-8744-EC134466AE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13890" xr2:uid="{0D4BA749-7C78-481F-A3B6-AB5C0B057229}"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13890" activeTab="1" xr2:uid="{0D4BA749-7C78-481F-A3B6-AB5C0B057229}"/>
   </bookViews>
   <sheets>
     <sheet name="Drivers, Inputs and Outputs" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="645">
   <si>
     <t>Term</t>
   </si>
@@ -2168,6 +2168,9 @@
   </si>
   <si>
     <t>Intrinsic Value/ Share</t>
+  </si>
+  <si>
+    <t>Needs Circularity switch</t>
   </si>
 </sst>
 </file>
@@ -3709,14 +3712,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4267,7 +4270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80524B63-3109-40A3-A0C1-4FF6BEC180EA}">
-  <dimension ref="A1:S125"/>
+  <dimension ref="A1:S129"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3.44140625" customWidth="1"/>
@@ -4464,7 +4467,7 @@
       </c>
       <c r="O10" s="6">
         <f>Model!P7*Model!P584</f>
-        <v>0</v>
+        <v>42115.131332452074</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>386</v>
@@ -4911,6 +4914,7 @@
         <f>Model!J81</f>
         <v>10727</v>
       </c>
+      <c r="Q41" s="22"/>
     </row>
     <row r="42" spans="1:17">
       <c r="B42" s="204" t="s">
@@ -5804,7 +5808,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="97" spans="2:17">
+    <row r="97" spans="1:17">
       <c r="B97" s="204" t="s">
         <v>412</v>
       </c>
@@ -5814,10 +5818,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:17">
+    <row r="99" spans="1:17">
       <c r="C99" s="23"/>
     </row>
-    <row r="100" spans="2:17">
+    <row r="100" spans="1:17">
       <c r="B100" s="321"/>
       <c r="C100" s="323"/>
       <c r="D100" s="321"/>
@@ -5834,10 +5838,13 @@
       <c r="O100" s="321"/>
       <c r="P100" s="321"/>
     </row>
-    <row r="101" spans="2:17">
+    <row r="101" spans="1:17">
       <c r="C101" s="23"/>
     </row>
-    <row r="102" spans="2:17">
+    <row r="102" spans="1:17">
+      <c r="A102" t="s">
+        <v>95</v>
+      </c>
       <c r="B102" s="356" t="s">
         <v>626</v>
       </c>
@@ -5856,31 +5863,31 @@
       <c r="O102" s="357"/>
       <c r="P102" s="356"/>
     </row>
-    <row r="107" spans="2:17">
+    <row r="107" spans="1:17">
       <c r="B107" s="78"/>
       <c r="C107" s="320"/>
-      <c r="D107" s="363" t="s">
+      <c r="D107" s="362" t="s">
         <v>629</v>
       </c>
-      <c r="E107" s="363"/>
-      <c r="F107" s="363"/>
-      <c r="G107" s="363"/>
-      <c r="H107" s="363"/>
-      <c r="L107" s="363" t="s">
+      <c r="E107" s="362"/>
+      <c r="F107" s="362"/>
+      <c r="G107" s="362"/>
+      <c r="H107" s="362"/>
+      <c r="L107" s="362" t="s">
         <v>632</v>
       </c>
-      <c r="M107" s="363"/>
-      <c r="N107" s="363"/>
-      <c r="O107" s="363"/>
-      <c r="P107" s="363"/>
-    </row>
-    <row r="108" spans="2:17">
+      <c r="M107" s="362"/>
+      <c r="N107" s="362"/>
+      <c r="O107" s="362"/>
+      <c r="P107" s="362"/>
+    </row>
+    <row r="108" spans="1:17">
       <c r="B108" s="17"/>
       <c r="E108" s="339"/>
       <c r="F108" s="339"/>
       <c r="G108" s="339"/>
     </row>
-    <row r="109" spans="2:17">
+    <row r="109" spans="1:17">
       <c r="E109" s="5"/>
       <c r="F109" s="340" t="s">
         <v>630</v>
@@ -5893,7 +5900,7 @@
       <c r="O109" s="5"/>
       <c r="Q109"/>
     </row>
-    <row r="110" spans="2:17">
+    <row r="110" spans="1:17">
       <c r="C110" s="338">
         <f ca="1">Model!J638</f>
         <v>817660.71828655864</v>
@@ -5939,8 +5946,8 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="111" spans="2:17">
-      <c r="B111" s="362" t="s">
+    <row r="111" spans="1:17">
+      <c r="B111" s="361" t="s">
         <v>343</v>
       </c>
       <c r="C111" s="240">
@@ -5967,7 +5974,7 @@
         <f>Model!H710</f>
         <v>1075840.0890928849</v>
       </c>
-      <c r="J111" s="362" t="s">
+      <c r="J111" s="361" t="s">
         <v>343</v>
       </c>
       <c r="K111" s="264">
@@ -5995,8 +6002,8 @@
         <v>129.8512218156925</v>
       </c>
     </row>
-    <row r="112" spans="2:17">
-      <c r="B112" s="362"/>
+    <row r="112" spans="1:17">
+      <c r="B112" s="361"/>
       <c r="C112" s="240">
         <f>Model!C711</f>
         <v>6.7500000000000004E-2</v>
@@ -6021,7 +6028,7 @@
         <f>Model!H711</f>
         <v>989593.04280312883</v>
       </c>
-      <c r="J112" s="362"/>
+      <c r="J112" s="361"/>
       <c r="K112" s="264">
         <f>C122</f>
         <v>6.7500000000000004E-2</v>
@@ -6048,7 +6055,7 @@
       </c>
     </row>
     <row r="113" spans="2:16">
-      <c r="B113" s="362"/>
+      <c r="B113" s="361"/>
       <c r="C113" s="240">
         <f>Model!C712</f>
         <v>6.9680317614409834E-2</v>
@@ -6073,7 +6080,7 @@
         <f>Model!H712</f>
         <v>924560.61988139967</v>
       </c>
-      <c r="J113" s="362"/>
+      <c r="J113" s="361"/>
       <c r="K113" s="264">
         <f>C123</f>
         <v>6.9680317614409834E-2</v>
@@ -6100,7 +6107,7 @@
       </c>
     </row>
     <row r="114" spans="2:16">
-      <c r="B114" s="362"/>
+      <c r="B114" s="361"/>
       <c r="C114" s="240">
         <f>Model!C713</f>
         <v>7.2499999999999995E-2</v>
@@ -6125,7 +6132,7 @@
         <f>Model!H713</f>
         <v>851715.36969656986</v>
       </c>
-      <c r="J114" s="362"/>
+      <c r="J114" s="361"/>
       <c r="K114" s="264">
         <f>C124</f>
         <v>7.2499999999999995E-2</v>
@@ -6152,7 +6159,7 @@
       </c>
     </row>
     <row r="115" spans="2:16">
-      <c r="B115" s="362"/>
+      <c r="B115" s="361"/>
       <c r="C115" s="240">
         <f>Model!C714</f>
         <v>7.4999999999999997E-2</v>
@@ -6177,7 +6184,7 @@
         <f>Model!H714</f>
         <v>795756.67296940694</v>
       </c>
-      <c r="J115" s="362"/>
+      <c r="J115" s="361"/>
       <c r="K115" s="264">
         <f>C125</f>
         <v>7.4999999999999997E-2</v>
@@ -6204,20 +6211,20 @@
       </c>
     </row>
     <row r="117" spans="2:16">
-      <c r="D117" s="363" t="s">
+      <c r="D117" s="362" t="s">
         <v>359</v>
       </c>
-      <c r="E117" s="363"/>
-      <c r="F117" s="363"/>
-      <c r="G117" s="363"/>
-      <c r="H117" s="363"/>
-      <c r="L117" s="363" t="s">
+      <c r="E117" s="362"/>
+      <c r="F117" s="362"/>
+      <c r="G117" s="362"/>
+      <c r="H117" s="362"/>
+      <c r="L117" s="362" t="s">
         <v>631</v>
       </c>
-      <c r="M117" s="363"/>
-      <c r="N117" s="363"/>
-      <c r="O117" s="363"/>
-      <c r="P117" s="363"/>
+      <c r="M117" s="362"/>
+      <c r="N117" s="362"/>
+      <c r="O117" s="362"/>
+      <c r="P117" s="362"/>
     </row>
     <row r="119" spans="2:16" ht="14.4" customHeight="1">
       <c r="E119" s="5"/>
@@ -6274,7 +6281,7 @@
       </c>
     </row>
     <row r="121" spans="2:16">
-      <c r="B121" s="362" t="s">
+      <c r="B121" s="361" t="s">
         <v>343</v>
       </c>
       <c r="C121" s="264">
@@ -6301,7 +6308,7 @@
         <f t="shared" si="7"/>
         <v>1035044.0890928849</v>
       </c>
-      <c r="J121" s="362" t="s">
+      <c r="J121" s="361" t="s">
         <v>343</v>
       </c>
       <c r="K121" s="264">
@@ -6330,7 +6337,7 @@
       </c>
     </row>
     <row r="122" spans="2:16">
-      <c r="B122" s="362"/>
+      <c r="B122" s="361"/>
       <c r="C122" s="264">
         <f>C112</f>
         <v>6.7500000000000004E-2</v>
@@ -6355,7 +6362,7 @@
         <f t="shared" si="7"/>
         <v>948797.04280312883</v>
       </c>
-      <c r="J122" s="362"/>
+      <c r="J122" s="361"/>
       <c r="K122" s="264">
         <f>C122</f>
         <v>6.7500000000000004E-2</v>
@@ -6382,7 +6389,7 @@
       </c>
     </row>
     <row r="123" spans="2:16">
-      <c r="B123" s="362"/>
+      <c r="B123" s="361"/>
       <c r="C123" s="264">
         <f>C113</f>
         <v>6.9680317614409834E-2</v>
@@ -6407,7 +6414,7 @@
         <f t="shared" si="7"/>
         <v>883764.61988139967</v>
       </c>
-      <c r="J123" s="362"/>
+      <c r="J123" s="361"/>
       <c r="K123" s="264">
         <f>C123</f>
         <v>6.9680317614409834E-2</v>
@@ -6434,7 +6441,7 @@
       </c>
     </row>
     <row r="124" spans="2:16">
-      <c r="B124" s="362"/>
+      <c r="B124" s="361"/>
       <c r="C124" s="264">
         <f>C114</f>
         <v>7.2499999999999995E-2</v>
@@ -6459,7 +6466,7 @@
         <f t="shared" si="7"/>
         <v>810919.36969656986</v>
       </c>
-      <c r="J124" s="362"/>
+      <c r="J124" s="361"/>
       <c r="K124" s="264">
         <f>C124</f>
         <v>7.2499999999999995E-2</v>
@@ -6486,7 +6493,7 @@
       </c>
     </row>
     <row r="125" spans="2:16">
-      <c r="B125" s="362"/>
+      <c r="B125" s="361"/>
       <c r="C125" s="264">
         <f>C115</f>
         <v>7.4999999999999997E-2</v>
@@ -6511,7 +6518,7 @@
         <f t="shared" si="7"/>
         <v>754960.67296940694</v>
       </c>
-      <c r="J125" s="362"/>
+      <c r="J125" s="361"/>
       <c r="K125" s="264">
         <f>C125</f>
         <v>7.4999999999999997E-2</v>
@@ -6535,6 +6542,11 @@
       <c r="P125" s="347">
         <f t="shared" si="12"/>
         <v>-0.17338610342421579</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -13060,7 +13072,7 @@
       </c>
       <c r="P216" s="36">
         <f>'Drivers, Inputs and Outputs'!O10</f>
-        <v>0</v>
+        <v>42115.131332452074</v>
       </c>
       <c r="R216" s="180" t="s">
         <v>537</v>
@@ -13769,7 +13781,7 @@
       </c>
       <c r="P257" s="36">
         <f>'Drivers, Inputs and Outputs'!O10</f>
-        <v>0</v>
+        <v>42115.131332452074</v>
       </c>
     </row>
     <row r="258" spans="2:16">
@@ -17072,7 +17084,7 @@
         <v>0</v>
       </c>
       <c r="R419" s="180" t="s">
-        <v>427</v>
+        <v>644</v>
       </c>
     </row>
     <row r="420" spans="2:18">
@@ -18578,7 +18590,7 @@
       </c>
       <c r="P489" s="14">
         <f>'Drivers, Inputs and Outputs'!O10</f>
-        <v>0</v>
+        <v>42115.131332452074</v>
       </c>
     </row>
     <row r="490" spans="2:16">
@@ -18610,7 +18622,7 @@
       </c>
       <c r="P490" s="14">
         <f t="shared" ref="P490" si="232">SUM(P488:P489)</f>
-        <v>49547.213332296466</v>
+        <v>91662.34466474854</v>
       </c>
     </row>
     <row r="492" spans="2:16">
@@ -18647,7 +18659,7 @@
       </c>
       <c r="P493" s="14">
         <f t="shared" ref="P493" si="233">P490</f>
-        <v>49547.213332296466</v>
+        <v>91662.34466474854</v>
       </c>
     </row>
     <row r="494" spans="2:16">
@@ -18711,7 +18723,7 @@
       </c>
       <c r="P495" s="14">
         <f>'Drivers, Inputs and Outputs'!O10*-1</f>
-        <v>0</v>
+        <v>-42115.131332452074</v>
       </c>
     </row>
     <row r="496" spans="2:16">
@@ -18879,7 +18891,7 @@
       </c>
       <c r="P502" s="14">
         <f t="shared" ref="P502" si="239">P489</f>
-        <v>0</v>
+        <v>42115.131332452074</v>
       </c>
     </row>
     <row r="503" spans="1:18">
@@ -18911,7 +18923,7 @@
       </c>
       <c r="P503" s="14">
         <f t="shared" si="240"/>
-        <v>0</v>
+        <v>-42115.131332452074</v>
       </c>
     </row>
     <row r="504" spans="1:18">
@@ -21154,7 +21166,9 @@
       <c r="O584" s="255">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="P584" s="255"/>
+      <c r="P584" s="255">
+        <v>4.2500000000000003E-2</v>
+      </c>
     </row>
     <row r="586" spans="2:30">
       <c r="B586" s="187" t="s">
@@ -23090,7 +23104,7 @@
       <c r="O660" s="297"/>
       <c r="P660" s="298">
         <f>P493</f>
-        <v>49547.213332296466</v>
+        <v>91662.34466474854</v>
       </c>
     </row>
     <row r="661" spans="2:16" ht="15.05" customHeight="1">
@@ -23194,7 +23208,7 @@
       </c>
       <c r="P664" s="76">
         <f>(P660*D654)/(1+D655)^F665</f>
-        <v>902074.80115085305</v>
+        <v>1668838.3821290794</v>
       </c>
     </row>
     <row r="665" spans="2:16" ht="15.05" customHeight="1">
@@ -23234,7 +23248,7 @@
       </c>
       <c r="P665" s="72">
         <f t="shared" si="311"/>
-        <v>941037.96543775569</v>
+        <v>1707801.5464159821</v>
       </c>
     </row>
     <row r="666" spans="2:16" ht="15.05" customHeight="1">
@@ -23392,7 +23406,7 @@
       </c>
       <c r="P671" s="76">
         <f t="shared" si="314"/>
-        <v>902074.80115085305</v>
+        <v>1668838.3821290794</v>
       </c>
     </row>
     <row r="672" spans="2:16" ht="15.05" customHeight="1">
@@ -23430,7 +23444,7 @@
       </c>
       <c r="P672" s="72">
         <f t="shared" si="315"/>
-        <v>941037.96543775569</v>
+        <v>1707801.5464159821</v>
       </c>
     </row>
     <row r="673" spans="2:16" ht="15.05" customHeight="1">
@@ -23588,7 +23602,7 @@
       </c>
       <c r="P678" s="98">
         <f t="shared" si="318"/>
-        <v>636937.56031017576</v>
+        <v>1178334.4865738261</v>
       </c>
     </row>
     <row r="679" spans="2:16" ht="15.05" customHeight="1">
@@ -23626,7 +23640,7 @@
       </c>
       <c r="P679" s="72">
         <f t="shared" si="319"/>
-        <v>664448.69660530682</v>
+        <v>1205845.6228689572</v>
       </c>
     </row>
     <row r="680" spans="2:16" ht="15.05" customHeight="1">
@@ -23693,7 +23707,7 @@
       <c r="I683" s="305"/>
       <c r="J683" s="306">
         <f ca="1">SUM(K679:P679)</f>
-        <v>740479.23702700005</v>
+        <v>1281876.1632906506</v>
       </c>
       <c r="K683" s="84"/>
       <c r="M683" s="169" t="s">
@@ -23702,7 +23716,7 @@
       <c r="N683" s="170"/>
       <c r="O683" s="307">
         <f ca="1">P683/$P$685</f>
-        <v>0.13983062797620194</v>
+        <v>8.0773540909776204E-2</v>
       </c>
       <c r="P683" s="306">
         <f ca="1">SUM(K677:P677)</f>
@@ -23721,7 +23735,7 @@
       <c r="I684" s="260"/>
       <c r="J684" s="309">
         <f ca="1">XNPV(D655,J672:P672,J657:P657)</f>
-        <v>740461.01435510349</v>
+        <v>1281841.2886338604</v>
       </c>
       <c r="K684" s="84"/>
       <c r="M684" s="174" t="s">
@@ -23730,11 +23744,11 @@
       <c r="N684" s="166"/>
       <c r="O684" s="310">
         <f ca="1">P684/$P$685</f>
-        <v>0.86016937202379806</v>
+        <v>0.91922645909022382</v>
       </c>
       <c r="P684" s="309">
         <f>SUM(K678:P678)</f>
-        <v>636937.56031017576</v>
+        <v>1178334.4865738261</v>
       </c>
     </row>
     <row r="685" spans="2:16" ht="15.05" customHeight="1">
@@ -23757,7 +23771,7 @@
       </c>
       <c r="P685" s="309">
         <f ca="1">SUM(P683:P684)</f>
-        <v>740479.23702700005</v>
+        <v>1281876.1632906504</v>
       </c>
     </row>
     <row r="686" spans="2:16" ht="15.05" customHeight="1">
@@ -23821,7 +23835,7 @@
       <c r="I689" s="311"/>
       <c r="J689" s="306">
         <f ca="1">J684</f>
-        <v>740461.01435510349</v>
+        <v>1281841.2886338604</v>
       </c>
       <c r="K689" s="154"/>
       <c r="M689" s="304" t="s">
@@ -23831,7 +23845,7 @@
       <c r="O689" s="311"/>
       <c r="P689" s="306">
         <f ca="1">J691</f>
-        <v>699665.01435510349</v>
+        <v>1241045.2886338604</v>
       </c>
     </row>
     <row r="690" spans="1:16" ht="15.05" customHeight="1">
@@ -23873,7 +23887,7 @@
       <c r="I691" s="260"/>
       <c r="J691" s="309">
         <f ca="1">SUM(J689:J690)</f>
-        <v>699665.01435510349</v>
+        <v>1241045.2886338604</v>
       </c>
       <c r="K691" s="154"/>
       <c r="M691" s="308" t="s">
@@ -23885,7 +23899,7 @@
       </c>
       <c r="P691" s="316">
         <f ca="1">P689/P690</f>
-        <v>87.776315939669232</v>
+        <v>155.6950556559855</v>
       </c>
     </row>
     <row r="692" spans="1:16" ht="15.05" customHeight="1">
@@ -24089,7 +24103,7 @@
       </c>
     </row>
     <row r="710" spans="2:16">
-      <c r="B710" s="361" t="s">
+      <c r="B710" s="363" t="s">
         <v>343</v>
       </c>
       <c r="C710" s="250">
@@ -24111,7 +24125,7 @@
       <c r="H710" s="325">
         <v>1075840.0890928849</v>
       </c>
-      <c r="J710" s="361" t="s">
+      <c r="J710" s="363" t="s">
         <v>343</v>
       </c>
       <c r="K710" s="250">
@@ -24140,7 +24154,7 @@
       </c>
     </row>
     <row r="711" spans="2:16">
-      <c r="B711" s="361"/>
+      <c r="B711" s="363"/>
       <c r="C711" s="250">
         <v>6.7500000000000004E-2</v>
       </c>
@@ -24159,7 +24173,7 @@
       <c r="H711" s="327">
         <v>989593.04280312883</v>
       </c>
-      <c r="J711" s="361"/>
+      <c r="J711" s="363"/>
       <c r="K711" s="250">
         <f t="shared" ref="K711:K714" si="322">C711</f>
         <v>6.7500000000000004E-2</v>
@@ -24186,7 +24200,7 @@
       </c>
     </row>
     <row r="712" spans="2:16">
-      <c r="B712" s="361"/>
+      <c r="B712" s="363"/>
       <c r="C712" s="250">
         <v>6.9680317614409834E-2</v>
       </c>
@@ -24205,7 +24219,7 @@
       <c r="H712" s="327">
         <v>924560.61988139967</v>
       </c>
-      <c r="J712" s="361"/>
+      <c r="J712" s="363"/>
       <c r="K712" s="250">
         <f t="shared" si="322"/>
         <v>6.9680317614409834E-2</v>
@@ -24232,7 +24246,7 @@
       </c>
     </row>
     <row r="713" spans="2:16">
-      <c r="B713" s="361"/>
+      <c r="B713" s="363"/>
       <c r="C713" s="250">
         <v>7.2499999999999995E-2</v>
       </c>
@@ -24251,7 +24265,7 @@
       <c r="H713" s="327">
         <v>851715.36969656986</v>
       </c>
-      <c r="J713" s="361"/>
+      <c r="J713" s="363"/>
       <c r="K713" s="250">
         <f t="shared" si="322"/>
         <v>7.2499999999999995E-2</v>
@@ -24278,7 +24292,7 @@
       </c>
     </row>
     <row r="714" spans="2:16">
-      <c r="B714" s="361"/>
+      <c r="B714" s="363"/>
       <c r="C714" s="250">
         <v>7.4999999999999997E-2</v>
       </c>
@@ -24297,7 +24311,7 @@
       <c r="H714" s="330">
         <v>795756.67296940694</v>
       </c>
-      <c r="J714" s="361"/>
+      <c r="J714" s="363"/>
       <c r="K714" s="250">
         <f t="shared" si="322"/>
         <v>7.4999999999999997E-2</v>
@@ -24400,7 +24414,7 @@
       </c>
     </row>
     <row r="720" spans="2:16">
-      <c r="B720" s="361" t="str">
+      <c r="B720" s="363" t="str">
         <f>B710</f>
         <v>WACC</v>
       </c>
@@ -24428,7 +24442,7 @@
         <f t="shared" si="329"/>
         <v>1035044.0890928849</v>
       </c>
-      <c r="J720" s="361" t="s">
+      <c r="J720" s="363" t="s">
         <v>343</v>
       </c>
       <c r="K720" s="17">
@@ -24457,7 +24471,7 @@
       </c>
     </row>
     <row r="721" spans="1:16">
-      <c r="B721" s="361"/>
+      <c r="B721" s="363"/>
       <c r="C721" s="17">
         <f t="shared" ref="C721:C724" si="331">C711</f>
         <v>6.7500000000000004E-2</v>
@@ -24482,7 +24496,7 @@
         <f t="shared" si="332"/>
         <v>948797.04280312883</v>
       </c>
-      <c r="J721" s="361"/>
+      <c r="J721" s="363"/>
       <c r="K721" s="17">
         <f t="shared" ref="K721:K724" si="333">C721</f>
         <v>6.7500000000000004E-2</v>
@@ -24509,7 +24523,7 @@
       </c>
     </row>
     <row r="722" spans="1:16">
-      <c r="B722" s="361" t="str">
+      <c r="B722" s="363" t="str">
         <f>B710</f>
         <v>WACC</v>
       </c>
@@ -24537,7 +24551,7 @@
         <f t="shared" si="335"/>
         <v>883764.61988139967</v>
       </c>
-      <c r="J722" s="361"/>
+      <c r="J722" s="363"/>
       <c r="K722" s="17">
         <f t="shared" si="333"/>
         <v>6.9680317614409834E-2</v>
@@ -24564,7 +24578,7 @@
       </c>
     </row>
     <row r="723" spans="1:16">
-      <c r="B723" s="361"/>
+      <c r="B723" s="363"/>
       <c r="C723" s="17">
         <f t="shared" si="331"/>
         <v>7.2499999999999995E-2</v>
@@ -24589,7 +24603,7 @@
         <f t="shared" si="337"/>
         <v>810919.36969656986</v>
       </c>
-      <c r="J723" s="361"/>
+      <c r="J723" s="363"/>
       <c r="K723" s="17">
         <f t="shared" si="333"/>
         <v>7.2499999999999995E-2</v>
@@ -24616,7 +24630,7 @@
       </c>
     </row>
     <row r="724" spans="1:16">
-      <c r="B724" s="361"/>
+      <c r="B724" s="363"/>
       <c r="C724" s="17">
         <f t="shared" si="331"/>
         <v>7.4999999999999997E-2</v>
@@ -24641,7 +24655,7 @@
         <f t="shared" si="339"/>
         <v>754960.67296940694</v>
       </c>
-      <c r="J724" s="361"/>
+      <c r="J724" s="363"/>
       <c r="K724" s="17">
         <f t="shared" si="333"/>
         <v>7.4999999999999997E-2</v>
